--- a/output/pdf_financials_xlsx/SCZ.xlsx
+++ b/output/pdf_financials_xlsx/SCZ.xlsx
@@ -1967,31 +1967,31 @@
         <v>0.009339</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>1.493</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>1.736</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>2.464</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>2.155</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>1.998</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>1.141</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>4.137</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>-14.647</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>25.959</v>
@@ -2022,31 +2022,31 @@
         <v>-2.807401</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.771000000000001</v>
+        <v>-7.278</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-28.505</v>
+        <v>-26.769</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-25.839</v>
+        <v>-23.375</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-28.545</v>
+        <v>-26.39</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.149</v>
+        <v>-3.151</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-20.656</v>
+        <v>-19.515</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-1.493</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-14.889</v>
+        <v>-10.752</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-13.992</v>
+        <v>-28.639</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>18.047</v>
@@ -2085,31 +2085,31 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-82.54281949934123</v>
+        <v>-68.49237718802937</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-329.8044660418836</v>
+        <v>-309.7188476223533</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-218.7521164917034</v>
+        <v>-197.8919742634609</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-250.4826254826255</v>
+        <v>-231.5724815724816</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-39.1529161280511</v>
+        <v>-23.96015512128355</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-70.95599601525197</v>
+        <v>-67.03651540654735</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>-4.510982868537934</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-27.91652604342445</v>
+        <v>-20.15974800314996</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-5.022362290645168</v>
+        <v>-10.27983373654853</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>7.182714044639731</v>
@@ -5996,34 +5996,34 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.009339</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.493</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.736</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.464</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2.155</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1.998</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1.141</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>4.137</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>14.647</v>
       </c>
       <c r="O100" s="3" t="n">
         <v>25.959</v>
@@ -35304,7 +35304,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -46702,7 +46702,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -51798,7 +51798,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -62502,7 +62502,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">

--- a/output/pdf_financials_xlsx/SCZ.xlsx
+++ b/output/pdf_financials_xlsx/SCZ.xlsx
@@ -1042,10 +1042,10 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.274</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.947</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1933,10 +1933,10 @@
         <v>-1.493</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-14.889</v>
+        <v>-15.163</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-13.992</v>
+        <v>-14.939</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-7.912</v>
@@ -2043,10 +2043,10 @@
         <v>-1.493</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-10.752</v>
+        <v>-11.026</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-28.639</v>
+        <v>-29.586</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>18.047</v>
@@ -2106,10 +2106,10 @@
         <v>-4.510982868537934</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-20.15974800314996</v>
+        <v>-20.67349158135523</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-10.27983373654853</v>
+        <v>-10.61975491216609</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>7.182714044639731</v>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>8.8e-05</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.183072</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>8.8e-05</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.183072</v>
@@ -28138,7 +28138,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">
@@ -68290,7 +68290,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">

--- a/output/pdf_financials_xlsx/SCZ.xlsx
+++ b/output/pdf_financials_xlsx/SCZ.xlsx
@@ -6668,10 +6668,10 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -47990,7 +47990,11 @@
           <t>Proceeds from disposal of plant and equipment</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SCZ.xlsx
+++ b/output/pdf_financials_xlsx/SCZ.xlsx
@@ -1296,10 +1296,10 @@
         <v>-4.004469</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.871</v>
+        <v>0.871</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.321</v>
+        <v>-1.321</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.281</v>
@@ -2613,22 +2613,22 @@
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.678</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>9.832000000000001</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>7.179</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>4.789</v>
       </c>
     </row>
     <row r="41">
@@ -2668,22 +2668,22 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>10.928</v>
+        <v>11.493</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>13.26</v>
+        <v>13.938</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>99.027</v>
+        <v>108.859</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99.104</v>
+        <v>106.283</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>66.752</v>
+        <v>67.661</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>99.854</v>
+        <v>104.643</v>
       </c>
     </row>
     <row r="42">
@@ -3053,22 +3053,22 @@
         <v>6.263</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.638</v>
+        <v>3.073</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.503</v>
+        <v>1.825</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>9.644</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>9.712</v>
+        <v>2.533</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>5.536</v>
+        <v>4.627</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.656</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="49">
@@ -3991,40 +3991,40 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>2.397</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>4.647</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>8.686</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>15.484</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>11.835</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>25.391</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>27.434</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>25.729</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>52.756</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>34.229</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>29.784</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>34.541</v>
       </c>
     </row>
     <row r="65">
@@ -4156,28 +4156,28 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.523</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>1.054</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.451</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.299</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>1.935</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>4.761</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.128</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>3.889</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>66.023</v>
@@ -4235,16 +4235,16 @@
         <v>36.888</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>66.023</v>
+        <v>118.779</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>74.631</v>
+        <v>108.86</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>55.853</v>
+        <v>85.637</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>38.781</v>
+        <v>73.322</v>
       </c>
     </row>
     <row r="69">
@@ -4620,16 +4620,16 @@
         <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>137.281</v>
+        <v>84.52500000000001</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>137.412</v>
+        <v>103.183</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>86.126</v>
+        <v>56.342</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>69.02200000000001</v>
+        <v>34.481</v>
       </c>
     </row>
     <row r="76">
@@ -6411,13 +6411,13 @@
         <v>1.485</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0.229</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>2.042</v>
       </c>
     </row>
     <row r="108">
@@ -6595,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.090516</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -6616,10 +6616,10 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.278</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -6802,7 +6802,7 @@
         <v>0</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0</v>
+        <v>-34.262</v>
       </c>
     </row>
     <row r="115">
@@ -7689,10 +7689,8 @@
       <c r="M129" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="N129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N129" s="3" t="n">
+        <v>-23.357</v>
       </c>
       <c r="O129" s="3" t="n">
         <v>-5.659</v>
@@ -7700,10 +7698,8 @@
       <c r="P129" s="3" t="n">
         <v>-2.546</v>
       </c>
-      <c r="Q129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q129" s="3" t="n">
+        <v>21.875</v>
       </c>
     </row>
     <row r="130">
@@ -7936,7 +7932,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.090516</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -7957,10 +7953,10 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.278</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -8043,21 +8039,17 @@
       <c r="M135" s="3" t="n">
         <v>-1.472</v>
       </c>
-      <c r="N135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N135" s="3" t="n">
+        <v>29.372</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>29.593</v>
+        <v>29.591</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>54.242</v>
-      </c>
-      <c r="Q135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>54.432</v>
+      </c>
+      <c r="Q135" s="3" t="n">
+        <v>79.11</v>
       </c>
     </row>
   </sheetData>
@@ -29872,7 +29864,11 @@
           <t>Share-based compensation expense 14</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -30878,7 +30874,11 @@
           <t>Net cash generated by operating activities</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -31154,7 +31154,11 @@
           <t>Purchases of marketable securities 20</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -33298,7 +33302,11 @@
           <t>Share-based compensation expense 21</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -34446,7 +34454,11 @@
           <t>Share-based compensation expense - - 229 - - 229</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -34920,7 +34932,11 @@
           <t>Share-based compensation expense - - 105 - - 105</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -40236,7 +40252,11 @@
           <t>Net cash generated by (used by) operating activities</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -41864,7 +41884,11 @@
           <t>Deferred income tax expense 23(a)</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -47806,7 +47830,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -48808,7 +48836,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -50396,7 +50428,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -54454,7 +54490,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
@@ -58380,7 +58420,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr">
         <is>
           <t>-</t>
@@ -77102,7 +77146,11 @@
           <t>Income tax recovery (expense) 23(a)</t>
         </is>
       </c>
-      <c r="D728" t="inlineStr"/>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E728" t="inlineStr">
         <is>
           <t>-</t>
